--- a/a_stock_data/verification_records/verification_summary.xlsx
+++ b/a_stock_data/verification_records/verification_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-03 23:48:49</t>
+          <t>2026-06-07 20:32:27</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -623,6 +623,168 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>a_stock_data/verification_records/2026-06-02_rebound_le_7_no_st/verification_20260603_234840.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-05_daily</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a_stock_data/verification_records/2026-06-05_daily</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-07 20:32:27</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>163</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>a_stock_data/verification_records/2026-06-05_daily/verification_20260607_202715.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-05_rebound_le_7_no_st</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>a_stock_data/verification_records/2026-06-05_rebound_le_7_no_st</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-07 20:32:27</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>a_stock_data/verification_records/2026-06-05_rebound_le_7_no_st/verification_20260607_202715.xlsx</t>
         </is>
       </c>
     </row>
